--- a/Advanced Reactor Materials/Fall2026/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2026/grading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A329ECC-BB6B-9743-B68A-979F6F47FDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCA6660-9004-F447-B82D-4078AD4CA5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22320" yWindow="5140" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Contacts" sheetId="2" r:id="rId1"/>
     <sheet name="Grades" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="89">
   <si>
     <t>Roster</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>enwilso4@ncsu.edu</t>
+  </si>
+  <si>
+    <t>Exam 1 Bonus</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="A2:P107"/>
+  <dimension ref="A2:Q107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -1048,18 +1051,15 @@
     <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C3">
         <v>0.2</v>
       </c>
-      <c r="D3">
-        <v>0.2</v>
-      </c>
       <c r="E3">
         <v>0.2</v>
       </c>
@@ -1069,13 +1069,16 @@
       <c r="G3">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="I4" t="s">
+      <c r="H3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>0</v>
       </c>
@@ -1083,426 +1086,531 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" t="s">
-        <v>10</v>
-      </c>
       <c r="J5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" t="s">
         <v>11</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>12</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>13</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>14</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>17</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>22</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>36</v>
       </c>
       <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="I6">
-        <f>(C6+C$30+C$31)*C$3</f>
-        <v>1.6</v>
+      <c r="D6">
+        <v>3</v>
       </c>
       <c r="J6">
-        <f>(D6+D$30+D$31)*D$3</f>
+        <f>(C6+D6+C$30+C$31)*C$3</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="K6">
+        <f>(E6+E$30+E$31)*E$3</f>
         <v>0</v>
       </c>
-      <c r="K6">
-        <f>(E6+E$30)*E$3</f>
+      <c r="L6">
+        <f t="shared" ref="L6:L12" si="0">(F6+F$30)*F$3</f>
         <v>0</v>
       </c>
-      <c r="L6">
-        <f>(F6+F$30+$F$31)*F$3</f>
+      <c r="M6">
+        <f>(G6+G$30+$G$31)*G$3</f>
         <v>0</v>
       </c>
-      <c r="M6">
-        <f>(G6+G$30)*G$3</f>
+      <c r="N6">
+        <f t="shared" ref="N6:N12" si="1">(H6+H$30)*H$3</f>
         <v>0</v>
       </c>
-      <c r="N6" s="3">
-        <f>SUM(I6:M6)</f>
-        <v>1.6</v>
-      </c>
-      <c r="O6" s="2" t="e">
-        <f>N6/(100*SUM(C4:G4))</f>
+      <c r="O6" s="3">
+        <f>SUM(J6:N6)</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="P6" s="2" t="e">
+        <f>O6/(100*SUM(C4:H4))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>39</v>
       </c>
       <c r="B7" t="s">
         <v>40</v>
       </c>
-      <c r="I7">
-        <f t="shared" ref="I7:I12" si="0">(C7+C$30+C$31)*C$3</f>
-        <v>1.6</v>
+      <c r="D7">
+        <v>3</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7:J12" si="1">(D7+D$30+D$31)*D$3</f>
+        <f t="shared" ref="J7:J27" si="2">(C7+D7+C$30+C$31)*C$3</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="K7">
+        <f t="shared" ref="K7:K12" si="3">(E7+E$30+E$31)*E$3</f>
         <v>0</v>
       </c>
-      <c r="K7">
-        <f>(E7+E$30)*E$3</f>
+      <c r="L7">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7">
-        <f>(F7+F$30+$F$31)*F$3</f>
+      <c r="M7">
+        <f>(G7+G$30+$G$31)*G$3</f>
         <v>0</v>
       </c>
-      <c r="M7">
-        <f>(G7+G$30)*G$3</f>
+      <c r="N7">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N7" s="3">
-        <f t="shared" ref="N7:N12" si="2">SUM(I7:M7)</f>
-        <v>1.6</v>
-      </c>
-      <c r="O7" s="2" t="e">
-        <f t="shared" ref="O7:O12" si="3">N7/(100*SUM(C5:G5))</f>
+      <c r="O7" s="3">
+        <f t="shared" ref="O7:O12" si="4">SUM(J7:N7)</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="P7" s="2" t="e">
+        <f>O7/(100*SUM(C5:H5))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>45</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
       </c>
-      <c r="I8">
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
         <f t="shared" si="0"/>
-        <v>1.6</v>
-      </c>
-      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f>(G8+G$30+$G$31)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K8">
-        <f>(E8+E$30)*E$3</f>
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <f>(F8+F$30+$F$31)*F$3</f>
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <f>(G8+G$30)*G$3</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
-        <f t="shared" ref="N8" si="4">SUM(I8:M8)</f>
-        <v>1.6</v>
-      </c>
-      <c r="O8" s="2" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <f t="shared" ref="O8" si="5">SUM(J8:N8)</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="P8" s="2">
+        <f>O8/(100*SUM(C6:H6))</f>
+        <v>2.0000000000000005E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="B9" t="s">
         <v>52</v>
       </c>
-      <c r="I9">
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
         <f t="shared" si="0"/>
-        <v>1.6</v>
-      </c>
-      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>(G9+G$30+$G$31)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K9">
-        <f>(E9+E$30)*E$3</f>
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <f>(F9+F$30+$F$31)*F$3</f>
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <f>(G9+G$30)*G$3</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.6</v>
-      </c>
-      <c r="O9" s="2" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O9" s="3">
+        <f t="shared" si="4"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="P9" s="2">
+        <f>O9/(100*SUM(C7:H7))</f>
+        <v>2.0000000000000005E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>54</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="I10">
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
         <f t="shared" si="0"/>
-        <v>1.6</v>
-      </c>
-      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f>(G10+G$30+$G$31)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K10">
-        <f>(E10+E$30)*E$3</f>
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <f>(F10+F$30+$F$31)*F$3</f>
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <f>(G10+G$30)*G$3</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <f t="shared" si="2"/>
-        <v>1.6</v>
-      </c>
-      <c r="O10" s="2" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O10" s="3">
+        <f t="shared" si="4"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="P10" s="2">
+        <f>O10/(100*SUM(C8:H8))</f>
+        <v>2.0000000000000005E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>63</v>
       </c>
       <c r="B11" t="s">
         <v>64</v>
       </c>
-      <c r="I11">
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
         <f t="shared" si="0"/>
-        <v>1.6</v>
-      </c>
-      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f>(G11+G$30+$G$31)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11">
-        <f>(E11+E$30)*E$3</f>
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <f>(F11+F$30+$F$31)*F$3</f>
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <f>(G11+G$30)*G$3</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="3">
-        <f t="shared" si="2"/>
-        <v>1.6</v>
-      </c>
-      <c r="O11" s="2" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O11" s="3">
+        <f t="shared" si="4"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="P11" s="2">
+        <f>O11/(100*SUM(C9:H9))</f>
+        <v>2.0000000000000005E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>77</v>
       </c>
       <c r="B12" t="s">
         <v>78</v>
       </c>
-      <c r="I12">
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L12">
         <f t="shared" si="0"/>
-        <v>1.6</v>
-      </c>
-      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f>(G12+G$30+$G$31)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12">
-        <f>(E12+E$30)*E$3</f>
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <f>(F12+F$30+$F$31)*F$3</f>
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <f>(G12+G$30)*G$3</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
-        <f t="shared" si="2"/>
-        <v>1.6</v>
-      </c>
-      <c r="O12" s="2" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O12" s="3">
+        <f t="shared" si="4"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="P12" s="2">
+        <f>O12/(100*SUM(C10:H10))</f>
+        <v>2.0000000000000005E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>80</v>
       </c>
       <c r="B13" t="s">
         <v>81</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O13" s="3"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>83</v>
       </c>
       <c r="B14" t="s">
         <v>84</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O14" s="3"/>
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>33</v>
       </c>
       <c r="B15" t="s">
         <v>86</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="N16" s="3"/>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O15" s="3"/>
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>33</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O18" s="3"/>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
       <c r="B19" t="s">
         <v>43</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O19" s="3"/>
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
         <v>49</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O20" s="3"/>
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>57</v>
       </c>
       <c r="B21" t="s">
         <v>58</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O21" s="3"/>
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>60</v>
       </c>
       <c r="B22" t="s">
         <v>61</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="2"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="J22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>66</v>
       </c>
       <c r="B23" t="s">
         <v>67</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="2"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O23" s="3"/>
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>69</v>
       </c>
       <c r="B24" t="s">
         <v>70</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O24" s="3"/>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>72</v>
       </c>
       <c r="B25" t="s">
         <v>73</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="2"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O25" s="3"/>
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>39</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O26" s="3"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>15</v>
       </c>
@@ -1510,10 +1618,7 @@
         <f>AVERAGE(C6:C16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D28" s="1" t="e">
-        <f>AVERAGE(D6:D16)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="D28" s="1"/>
       <c r="E28" s="1" t="e">
         <f>AVERAGE(E6:E16)</f>
         <v>#DIV/0!</v>
@@ -1526,15 +1631,19 @@
         <f>AVERAGE(G6:G16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N28" t="s">
+      <c r="H28" s="1" t="e">
+        <f>AVERAGE(H6:H16)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O28" t="s">
         <v>24</v>
       </c>
-      <c r="O28" s="2" t="e">
-        <f>AVERAGE(O6:O16)</f>
+      <c r="P28" s="2" t="e">
+        <f>AVERAGE(P6:P16)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>23</v>
       </c>
@@ -1542,10 +1651,7 @@
         <f>STDEV(C6:C16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D29" s="1" t="e">
-        <f>STDEV(D6:D16)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="D29" s="1"/>
       <c r="E29" s="1" t="e">
         <f>STDEV(E6:E16)</f>
         <v>#DIV/0!</v>
@@ -1558,31 +1664,32 @@
         <f>STDEV(G6:G16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N29" t="s">
+      <c r="H29" s="1" t="e">
+        <f>STDEV(H6:H16)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O29" t="s">
         <v>25</v>
       </c>
-      <c r="O29" s="2" t="e">
-        <f>STDEV(O6:O16)</f>
+      <c r="P29" s="2" t="e">
+        <f>STDEV(P6:P16)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>16</v>
       </c>
       <c r="C30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>27</v>
       </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>17</v>
       </c>
@@ -1590,20 +1697,21 @@
         <f>C28+C30+C31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D32" s="1" t="e">
-        <f t="shared" ref="C32:E32" si="5">D28+D30+D31</f>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1" t="e">
+        <f t="shared" ref="E32:F32" si="6">E28+E30+E31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E32" s="1" t="e">
-        <f t="shared" si="5"/>
+      <c r="F32" s="1" t="e">
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F32" s="1" t="e">
-        <f>F28+F30+F31</f>
+      <c r="G32" s="1" t="e">
+        <f>G28+G30+G31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G32" s="1" t="e">
-        <f>G28+G30</f>
+      <c r="H32" s="1" t="e">
+        <f>H28+H30</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2001,39 +2109,39 @@
         <v>100</v>
       </c>
       <c r="D47">
-        <f t="shared" ref="D47:L47" si="6">SUM(D37:D46)</f>
+        <f t="shared" ref="D47:L47" si="7">SUM(D37:D46)</f>
         <v>95</v>
       </c>
       <c r="E47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
       <c r="F47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>89</v>
       </c>
       <c r="G47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>84</v>
       </c>
       <c r="H47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>74</v>
       </c>
       <c r="I47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
       <c r="J47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>91</v>
       </c>
       <c r="K47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>97</v>
       </c>
       <c r="L47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>83</v>
       </c>
     </row>
@@ -2431,39 +2539,39 @@
         <v>100</v>
       </c>
       <c r="D60">
-        <f t="shared" ref="D60:L60" si="7">SUM(D50:D59)</f>
+        <f t="shared" ref="D60:L60" si="8">SUM(D50:D59)</f>
         <v>93</v>
       </c>
       <c r="E60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>91</v>
       </c>
       <c r="F60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="G60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>68</v>
       </c>
       <c r="H60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>73</v>
       </c>
       <c r="I60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>88</v>
       </c>
       <c r="J60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="K60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="L60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>79</v>
       </c>
     </row>
@@ -2931,39 +3039,39 @@
         <v>100</v>
       </c>
       <c r="D75">
-        <f t="shared" ref="D75:L75" si="8">SUM(D63:D74)</f>
+        <f t="shared" ref="D75:L75" si="9">SUM(D63:D74)</f>
         <v>95</v>
       </c>
       <c r="E75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>89</v>
       </c>
       <c r="F75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="G75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>83</v>
       </c>
       <c r="H75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="I75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>83</v>
       </c>
       <c r="J75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="K75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>94</v>
       </c>
       <c r="L75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
     </row>
@@ -3463,39 +3571,39 @@
         <v>100</v>
       </c>
       <c r="D91">
-        <f t="shared" ref="D91:L91" si="9">SUM(D78:D89)</f>
+        <f t="shared" ref="D91:L91" si="10">SUM(D78:D89)</f>
         <v>92</v>
       </c>
       <c r="E91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>90</v>
       </c>
       <c r="F91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>84</v>
       </c>
       <c r="G91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>74</v>
       </c>
       <c r="H91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>68</v>
       </c>
       <c r="I91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>81</v>
       </c>
       <c r="J91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>85</v>
       </c>
       <c r="K91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>95</v>
       </c>
       <c r="L91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>78</v>
       </c>
     </row>

--- a/Advanced Reactor Materials/Fall2026/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCA6660-9004-F447-B82D-4078AD4CA5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A11BE3-BBE8-AA43-8360-661DE8D1C746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22320" yWindow="5140" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="2200" yWindow="5480" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="89">
   <si>
     <t>Roster</t>
   </si>
@@ -1043,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="A2:Q107"/>
+  <dimension ref="A2:W107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -1148,11 +1148,11 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <f>(G6+G$30+$G$31)*G$3</f>
+        <f t="shared" ref="M6:M12" si="1">(G6+G$30+$G$31)*G$3</f>
         <v>0</v>
       </c>
       <c r="N6">
-        <f t="shared" ref="N6:N12" si="1">(H6+H$30)*H$3</f>
+        <f t="shared" ref="N6:N12" si="2">(H6+H$30)*H$3</f>
         <v>0</v>
       </c>
       <c r="O6" s="3">
@@ -1160,7 +1160,7 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="P6" s="2" t="e">
-        <f>O6/(100*SUM(C4:H4))</f>
+        <f t="shared" ref="P6:P12" si="3">O6/(100*SUM(C4:H4))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1175,11 +1175,11 @@
         <v>3</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7:J27" si="2">(C7+D7+C$30+C$31)*C$3</f>
+        <f t="shared" ref="J7:J26" si="4">(C7+D7+C$30+C$31)*C$3</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="K7">
-        <f t="shared" ref="K7:K12" si="3">(E7+E$30+E$31)*E$3</f>
+        <f t="shared" ref="K7:K12" si="5">(E7+E$30+E$31)*E$3</f>
         <v>0</v>
       </c>
       <c r="L7">
@@ -1187,19 +1187,19 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <f>(G7+G$30+$G$31)*G$3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O7" s="3">
-        <f t="shared" ref="O7:O12" si="4">SUM(J7:N7)</f>
+        <f t="shared" ref="O7:O12" si="6">SUM(J7:N7)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="P7" s="2" t="e">
-        <f>O7/(100*SUM(C5:H5))</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1214,11 +1214,11 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="K8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L8">
@@ -1226,19 +1226,19 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <f>(G8+G$30+$G$31)*G$3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <f t="shared" ref="O8" si="5">SUM(J8:N8)</f>
+        <f t="shared" ref="O8" si="7">SUM(J8:N8)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="P8" s="2">
-        <f>O8/(100*SUM(C6:H6))</f>
+        <f t="shared" si="3"/>
         <v>2.0000000000000005E-3</v>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="K9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L9">
@@ -1265,19 +1265,19 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <f>(G9+G$30+$G$31)*G$3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="P9" s="2">
-        <f>O9/(100*SUM(C7:H7))</f>
+        <f t="shared" si="3"/>
         <v>2.0000000000000005E-3</v>
       </c>
     </row>
@@ -1292,11 +1292,11 @@
         <v>3</v>
       </c>
       <c r="J10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="K10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L10">
@@ -1304,19 +1304,19 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <f>(G10+G$30+$G$31)*G$3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O10" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="P10" s="2">
-        <f>O10/(100*SUM(C8:H8))</f>
+        <f t="shared" si="3"/>
         <v>2.0000000000000005E-3</v>
       </c>
     </row>
@@ -1331,11 +1331,11 @@
         <v>3</v>
       </c>
       <c r="J11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="K11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L11">
@@ -1343,19 +1343,19 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <f>(G11+G$30+$G$31)*G$3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O11" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="P11" s="2">
-        <f>O11/(100*SUM(C9:H9))</f>
+        <f t="shared" si="3"/>
         <v>2.0000000000000005E-3</v>
       </c>
     </row>
@@ -1370,11 +1370,11 @@
         <v>3</v>
       </c>
       <c r="J12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="K12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L12">
@@ -1382,19 +1382,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <f>(G12+G$30+$G$31)*G$3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="P12" s="2">
-        <f>O12/(100*SUM(C10:H10))</f>
+        <f t="shared" si="3"/>
         <v>2.0000000000000005E-3</v>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="J13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O13" s="3"/>
@@ -1426,7 +1426,7 @@
         <v>3</v>
       </c>
       <c r="J14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O14" s="3"/>
@@ -1443,7 +1443,7 @@
         <v>3</v>
       </c>
       <c r="J15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O15" s="3"/>
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="J18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O18" s="3"/>
@@ -1488,7 +1488,7 @@
         <v>3</v>
       </c>
       <c r="J19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O19" s="3"/>
@@ -1505,7 +1505,7 @@
         <v>3</v>
       </c>
       <c r="J20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O20" s="3"/>
@@ -1522,7 +1522,7 @@
         <v>3</v>
       </c>
       <c r="J21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O21" s="3"/>
@@ -1536,7 +1536,7 @@
         <v>61</v>
       </c>
       <c r="J22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O22" s="3"/>
@@ -1553,7 +1553,7 @@
         <v>3</v>
       </c>
       <c r="J23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O23" s="3"/>
@@ -1570,7 +1570,7 @@
         <v>3</v>
       </c>
       <c r="J24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O24" s="3"/>
@@ -1587,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="J25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O25" s="3"/>
@@ -1604,7 +1604,7 @@
         <v>3</v>
       </c>
       <c r="J26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="O26" s="3"/>
@@ -1699,11 +1699,11 @@
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="e">
-        <f t="shared" ref="E32:F32" si="6">E28+E30+E31</f>
+        <f t="shared" ref="E32:F32" si="8">E28+E30+E31</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F32" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G32" s="1" t="e">
@@ -1715,7 +1715,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>10</v>
       </c>
@@ -1723,384 +1723,141 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E36" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G36" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="H36" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="I36" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="J36" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="L36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="M36" t="s">
+        <v>86</v>
+      </c>
+      <c r="O36" t="s">
+        <v>34</v>
+      </c>
+      <c r="P36" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>49</v>
+      </c>
+      <c r="R36" t="s">
+        <v>58</v>
+      </c>
+      <c r="S36" t="s">
+        <v>61</v>
+      </c>
+      <c r="T36" t="s">
+        <v>67</v>
+      </c>
+      <c r="U36" t="s">
+        <v>70</v>
+      </c>
+      <c r="V36" t="s">
+        <v>73</v>
+      </c>
+      <c r="W36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>8</v>
-      </c>
-      <c r="D37">
-        <v>7</v>
-      </c>
-      <c r="E37">
-        <v>8</v>
-      </c>
-      <c r="F37">
-        <v>7</v>
-      </c>
-      <c r="G37">
-        <v>7</v>
-      </c>
-      <c r="H37">
-        <v>7</v>
-      </c>
-      <c r="I37">
-        <v>8</v>
-      </c>
-      <c r="J37">
-        <v>8</v>
-      </c>
-      <c r="K37">
-        <v>8</v>
-      </c>
-      <c r="L37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38">
-        <v>10</v>
-      </c>
-      <c r="D38">
-        <v>10</v>
-      </c>
-      <c r="E38">
-        <v>10</v>
-      </c>
-      <c r="F38">
-        <v>10</v>
-      </c>
-      <c r="G38">
-        <v>10</v>
-      </c>
-      <c r="H38">
-        <v>10</v>
-      </c>
-      <c r="I38">
-        <v>10</v>
-      </c>
-      <c r="J38">
-        <v>9</v>
-      </c>
-      <c r="K38">
-        <v>10</v>
-      </c>
-      <c r="L38">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>3</v>
       </c>
       <c r="C39">
-        <v>10</v>
-      </c>
-      <c r="D39">
-        <v>10</v>
-      </c>
-      <c r="E39">
-        <v>10</v>
-      </c>
-      <c r="F39">
-        <v>10</v>
-      </c>
-      <c r="G39">
-        <v>10</v>
-      </c>
-      <c r="H39">
-        <v>7</v>
-      </c>
-      <c r="I39">
-        <v>10</v>
-      </c>
-      <c r="J39">
-        <v>10</v>
-      </c>
-      <c r="K39">
-        <v>10</v>
-      </c>
-      <c r="L39">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>4</v>
       </c>
       <c r="C40">
-        <v>15</v>
-      </c>
-      <c r="D40">
-        <v>15</v>
-      </c>
-      <c r="E40">
-        <v>14</v>
-      </c>
-      <c r="F40">
-        <v>14</v>
-      </c>
-      <c r="G40">
-        <v>12</v>
-      </c>
-      <c r="H40">
-        <v>12</v>
-      </c>
-      <c r="I40">
-        <v>13</v>
-      </c>
-      <c r="J40">
-        <v>14</v>
-      </c>
-      <c r="K40">
-        <v>15</v>
-      </c>
-      <c r="L40">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>5</v>
       </c>
       <c r="C41">
         <v>10</v>
       </c>
-      <c r="D41">
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43">
         <v>9</v>
       </c>
-      <c r="E41">
-        <v>8</v>
-      </c>
-      <c r="F41">
-        <v>9</v>
-      </c>
-      <c r="G41">
-        <v>10</v>
-      </c>
-      <c r="H41">
-        <v>8</v>
-      </c>
-      <c r="I41">
-        <v>8</v>
-      </c>
-      <c r="J41">
-        <v>9</v>
-      </c>
-      <c r="K41">
-        <v>9</v>
-      </c>
-      <c r="L41">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42">
-        <v>6</v>
-      </c>
-      <c r="C42">
-        <v>10</v>
-      </c>
-      <c r="D42">
-        <v>9</v>
-      </c>
-      <c r="E42">
-        <v>8</v>
-      </c>
-      <c r="F42">
-        <v>8</v>
-      </c>
-      <c r="G42">
-        <v>5</v>
-      </c>
-      <c r="H42">
-        <v>8</v>
-      </c>
-      <c r="I42">
-        <v>8</v>
-      </c>
-      <c r="J42">
-        <v>8</v>
-      </c>
-      <c r="K42">
-        <v>8</v>
-      </c>
-      <c r="L42">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43">
-        <v>7</v>
-      </c>
-      <c r="C43">
-        <v>15</v>
-      </c>
-      <c r="D43">
-        <v>15</v>
-      </c>
-      <c r="E43">
-        <v>15</v>
-      </c>
-      <c r="F43">
-        <v>13</v>
-      </c>
-      <c r="G43">
-        <v>11</v>
-      </c>
-      <c r="H43">
-        <v>7</v>
-      </c>
-      <c r="I43">
-        <v>12</v>
-      </c>
-      <c r="J43">
-        <v>13</v>
-      </c>
-      <c r="K43">
-        <v>15</v>
-      </c>
-      <c r="L43">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>8</v>
       </c>
       <c r="C44">
-        <v>9</v>
-      </c>
-      <c r="D44">
-        <v>9</v>
-      </c>
-      <c r="E44">
-        <v>9</v>
-      </c>
-      <c r="F44">
-        <v>9</v>
-      </c>
-      <c r="G44">
-        <v>9</v>
-      </c>
-      <c r="H44">
-        <v>6</v>
-      </c>
-      <c r="I44">
-        <v>9</v>
-      </c>
-      <c r="J44">
-        <v>9</v>
-      </c>
-      <c r="K44">
-        <v>9</v>
-      </c>
-      <c r="L44">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>9</v>
       </c>
       <c r="C45">
-        <v>5</v>
-      </c>
-      <c r="D45">
-        <v>5</v>
-      </c>
-      <c r="E45">
-        <v>4</v>
-      </c>
-      <c r="F45">
-        <v>5</v>
-      </c>
-      <c r="G45">
-        <v>5</v>
-      </c>
-      <c r="H45">
-        <v>5</v>
-      </c>
-      <c r="I45">
-        <v>5</v>
-      </c>
-      <c r="J45">
-        <v>5</v>
-      </c>
-      <c r="K45">
-        <v>5</v>
-      </c>
-      <c r="L45">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>10</v>
       </c>
-      <c r="C46">
-        <v>8</v>
-      </c>
-      <c r="D46">
-        <v>6</v>
-      </c>
-      <c r="E46">
-        <v>8</v>
-      </c>
-      <c r="F46">
-        <v>4</v>
-      </c>
-      <c r="G46">
-        <v>5</v>
-      </c>
-      <c r="H46">
-        <v>4</v>
-      </c>
-      <c r="I46">
-        <v>7</v>
-      </c>
-      <c r="J46">
-        <v>6</v>
-      </c>
-      <c r="K46">
-        <v>8</v>
-      </c>
-      <c r="L46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>21</v>
       </c>
@@ -2109,40 +1866,40 @@
         <v>100</v>
       </c>
       <c r="D47">
-        <f t="shared" ref="D47:L47" si="7">SUM(D37:D46)</f>
-        <v>95</v>
+        <f t="shared" ref="D47:L47" si="9">SUM(D37:D46)</f>
+        <v>0</v>
       </c>
       <c r="E47">
-        <f t="shared" si="7"/>
-        <v>94</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="F47">
-        <f t="shared" si="7"/>
-        <v>89</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="G47">
-        <f t="shared" si="7"/>
-        <v>84</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="H47">
-        <f t="shared" si="7"/>
-        <v>74</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I47">
-        <f t="shared" si="7"/>
-        <v>90</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="J47">
-        <f t="shared" si="7"/>
-        <v>91</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="K47">
-        <f t="shared" si="7"/>
-        <v>97</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="L47">
-        <f t="shared" si="7"/>
-        <v>83</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
@@ -2539,39 +2296,39 @@
         <v>100</v>
       </c>
       <c r="D60">
-        <f t="shared" ref="D60:L60" si="8">SUM(D50:D59)</f>
+        <f t="shared" ref="D60:L60" si="10">SUM(D50:D59)</f>
         <v>93</v>
       </c>
       <c r="E60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>91</v>
       </c>
       <c r="F60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>93</v>
       </c>
       <c r="G60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>68</v>
       </c>
       <c r="H60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>73</v>
       </c>
       <c r="I60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
       <c r="J60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>97</v>
       </c>
       <c r="K60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>97</v>
       </c>
       <c r="L60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>79</v>
       </c>
     </row>
@@ -3039,39 +2796,39 @@
         <v>100</v>
       </c>
       <c r="D75">
-        <f t="shared" ref="D75:L75" si="9">SUM(D63:D74)</f>
+        <f t="shared" ref="D75:L75" si="11">SUM(D63:D74)</f>
         <v>95</v>
       </c>
       <c r="E75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>89</v>
       </c>
       <c r="F75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>90</v>
       </c>
       <c r="G75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>83</v>
       </c>
       <c r="H75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>77</v>
       </c>
       <c r="I75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>83</v>
       </c>
       <c r="J75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="K75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="L75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>85</v>
       </c>
     </row>
@@ -3571,39 +3328,39 @@
         <v>100</v>
       </c>
       <c r="D91">
-        <f t="shared" ref="D91:L91" si="10">SUM(D78:D89)</f>
+        <f t="shared" ref="D91:L91" si="12">SUM(D78:D89)</f>
         <v>92</v>
       </c>
       <c r="E91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>90</v>
       </c>
       <c r="F91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="G91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>74</v>
       </c>
       <c r="H91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>68</v>
       </c>
       <c r="I91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>81</v>
       </c>
       <c r="J91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>85</v>
       </c>
       <c r="K91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>95</v>
       </c>
       <c r="L91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>78</v>
       </c>
     </row>
